--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.22177624462012</v>
+        <v>3.93603863975077</v>
       </c>
       <c r="D2" t="n">
-        <v>8.707094143257514</v>
+        <v>1.414902798279346</v>
       </c>
       <c r="E2" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F2" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.26002591727638</v>
+        <v>4.917254211557412</v>
       </c>
       <c r="D3" t="n">
-        <v>18.93466675012452</v>
+        <v>3.076883346895234</v>
       </c>
       <c r="E3" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F3" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.08886460845583</v>
+        <v>6.839440498874072</v>
       </c>
       <c r="D4" t="n">
-        <v>28.43751873947262</v>
+        <v>4.6210967951643</v>
       </c>
       <c r="E4" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F4" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.19507368912892</v>
+        <v>5.556699474483449</v>
       </c>
       <c r="D5" t="n">
-        <v>19.01512657281689</v>
+        <v>3.089958068082744</v>
       </c>
       <c r="E5" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F5" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.2674929891772</v>
+        <v>4.268467610741296</v>
       </c>
       <c r="D6" t="n">
-        <v>19.92485884517128</v>
+        <v>3.237789562340332</v>
       </c>
       <c r="E6" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F6" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.583583574943004</v>
+        <v>1.394832330928238</v>
       </c>
       <c r="D7" t="n">
-        <v>1.504119257125542</v>
+        <v>0.2444193792829006</v>
       </c>
       <c r="E7" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F7" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.39257588361102</v>
+        <v>3.151293581086791</v>
       </c>
       <c r="D8" t="n">
-        <v>18.42062166189073</v>
+        <v>2.993351020057244</v>
       </c>
       <c r="E8" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F8" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.52562418976663</v>
+        <v>3.172913930837078</v>
       </c>
       <c r="D9" t="n">
-        <v>21.91177536237117</v>
+        <v>3.560663496385316</v>
       </c>
       <c r="E9" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F9" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.23494916603094</v>
+        <v>7.188179239480029</v>
       </c>
       <c r="D10" t="n">
-        <v>44.43320811064281</v>
+        <v>7.220396317979457</v>
       </c>
       <c r="E10" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F10" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.87474252701249</v>
+        <v>6.479645660639529</v>
       </c>
       <c r="D11" t="n">
-        <v>17.00735135169495</v>
+        <v>2.763694594650429</v>
       </c>
       <c r="E11" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F11" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.04786719205747</v>
+        <v>4.395278418709339</v>
       </c>
       <c r="D12" t="n">
-        <v>3.354101966249685</v>
+        <v>0.5450415695155738</v>
       </c>
       <c r="E12" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F12" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.890408147485404</v>
+        <v>1.607191323966378</v>
       </c>
       <c r="D13" t="n">
-        <v>15.95131481867386</v>
+        <v>2.592088658034503</v>
       </c>
       <c r="E13" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F13" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.30490987333343</v>
+        <v>5.087047854416682</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34236310888167</v>
+        <v>5.093134005193272</v>
       </c>
       <c r="E14" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F14" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.90174920373668</v>
+        <v>2.259034245607211</v>
       </c>
       <c r="D15" t="n">
-        <v>15.52417469626002</v>
+        <v>2.522678388142254</v>
       </c>
       <c r="E15" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F15" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.30843939372317</v>
+        <v>5.087621401480015</v>
       </c>
       <c r="D16" t="n">
-        <v>4.609772228646444</v>
+        <v>0.7490879871550471</v>
       </c>
       <c r="E16" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F16" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.86935141995883</v>
+        <v>6.153769605743309</v>
       </c>
       <c r="D17" t="n">
-        <v>14.5878700264673</v>
+        <v>2.370528879300936</v>
       </c>
       <c r="E17" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F17" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>23.30152483520589</v>
+        <v>3.786497785720957</v>
       </c>
       <c r="D18" t="n">
-        <v>23.26450875981123</v>
+        <v>3.780482673469325</v>
       </c>
       <c r="E18" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F18" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>32.20015695697094</v>
+        <v>5.232525505507779</v>
       </c>
       <c r="D19" t="n">
-        <v>32.37700344572601</v>
+        <v>5.261263059930477</v>
       </c>
       <c r="E19" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F19" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>27.56687154844265</v>
+        <v>4.479616626621931</v>
       </c>
       <c r="D20" t="n">
-        <v>15.50806241927082</v>
+        <v>2.520060143131509</v>
       </c>
       <c r="E20" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F20" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>14.72121198654794</v>
+        <v>2.392196947814041</v>
       </c>
       <c r="D21" t="n">
-        <v>14.91866549079534</v>
+        <v>2.424283142254243</v>
       </c>
       <c r="E21" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F21" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>8.138807090041004</v>
+        <v>1.322556152131663</v>
       </c>
       <c r="D22" t="n">
-        <v>8.419002029281735</v>
+        <v>1.368087829758282</v>
       </c>
       <c r="E22" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F22" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>15.80304869151084</v>
+        <v>2.567995412370511</v>
       </c>
       <c r="D23" t="n">
-        <v>16.10072177273401</v>
+        <v>2.616367288069277</v>
       </c>
       <c r="E23" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F23" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>4.060601579065119</v>
+        <v>0.6598477565980818</v>
       </c>
       <c r="D24" t="n">
-        <v>4.145033308711809</v>
+        <v>0.673567912665669</v>
       </c>
       <c r="E24" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F24" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>39.36183683522709</v>
+        <v>6.396298485724403</v>
       </c>
       <c r="D25" t="n">
-        <v>17.37817427632807</v>
+        <v>2.823953319903312</v>
       </c>
       <c r="E25" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F25" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>43.17151176394724</v>
+        <v>7.015370661641426</v>
       </c>
       <c r="D26" t="n">
-        <v>9.290757698982164</v>
+        <v>1.509748126084602</v>
       </c>
       <c r="E26" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F26" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>12.77348384270642</v>
+        <v>2.075691124439794</v>
       </c>
       <c r="D27" t="n">
-        <v>13.03578078174435</v>
+        <v>2.118314377033458</v>
       </c>
       <c r="E27" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F27" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>21.86393866279304</v>
+        <v>3.552890032703869</v>
       </c>
       <c r="D28" t="n">
-        <v>21.5815594391696</v>
+        <v>3.507003408865061</v>
       </c>
       <c r="E28" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F28" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>52.86125757029431</v>
+        <v>8.589954355172827</v>
       </c>
       <c r="D29" t="n">
-        <v>16.48984603391499</v>
+        <v>2.679599980511187</v>
       </c>
       <c r="E29" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F29" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>35.82452917381313</v>
+        <v>5.821485990744634</v>
       </c>
       <c r="D30" t="n">
-        <v>24.63099724484919</v>
+        <v>4.002537052287993</v>
       </c>
       <c r="E30" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F30" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>18.26852586380861</v>
+        <v>2.968635452868899</v>
       </c>
       <c r="D31" t="n">
-        <v>18.39673382269742</v>
+        <v>2.989469246188332</v>
       </c>
       <c r="E31" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F31" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>61.64726354849667</v>
+        <v>10.01768032663071</v>
       </c>
       <c r="D32" t="n">
-        <v>29.47032405658275</v>
+        <v>4.788927659194697</v>
       </c>
       <c r="E32" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F32" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>52.00238646320327</v>
+        <v>8.450387800270532</v>
       </c>
       <c r="D33" t="n">
-        <v>20.69318094244516</v>
+        <v>3.362641903147338</v>
       </c>
       <c r="E33" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F33" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>38.77441660237082</v>
+        <v>6.300842697885258</v>
       </c>
       <c r="D34" t="n">
-        <v>33.56173039702081</v>
+        <v>5.453781189515881</v>
       </c>
       <c r="E34" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F34" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>58.24633774401092</v>
+        <v>9.465029883401776</v>
       </c>
       <c r="D35" t="n">
-        <v>35.09652141763311</v>
+        <v>5.70318473036538</v>
       </c>
       <c r="E35" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F35" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>63.82268487086366</v>
+        <v>10.37118629151534</v>
       </c>
       <c r="D36" t="n">
-        <v>34.94303399820915</v>
+        <v>5.678243024708986</v>
       </c>
       <c r="E36" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F36" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>34.28691473931545</v>
+        <v>5.571623645138761</v>
       </c>
       <c r="D37" t="n">
-        <v>33.98952351869012</v>
+        <v>5.523297571787145</v>
       </c>
       <c r="E37" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F37" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>19.32121162940807</v>
+        <v>3.139696889778811</v>
       </c>
       <c r="D38" t="n">
-        <v>19.08677278942526</v>
+        <v>3.101600578281604</v>
       </c>
       <c r="E38" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F38" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>29.08424118997716</v>
+        <v>4.726189193371288</v>
       </c>
       <c r="D39" t="n">
-        <v>22.3773460161645</v>
+        <v>3.636318727626731</v>
       </c>
       <c r="E39" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F39" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>38.4340383414452</v>
+        <v>6.245531230484845</v>
       </c>
       <c r="D40" t="n">
-        <v>23.141858497691</v>
+        <v>3.760552005874788</v>
       </c>
       <c r="E40" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F40" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>75.38575806737042</v>
+        <v>12.25018568594769</v>
       </c>
       <c r="D41" t="n">
-        <v>51.90857347298228</v>
+        <v>8.435143189359621</v>
       </c>
       <c r="E41" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F41" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>38.48781610555783</v>
+        <v>6.254270117153147</v>
       </c>
       <c r="D42" t="n">
-        <v>13.01850652582894</v>
+        <v>2.115507310447203</v>
       </c>
       <c r="E42" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F42" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>87.41447393521203</v>
+        <v>14.20485201447196</v>
       </c>
       <c r="D43" t="n">
-        <v>64.89483580054923</v>
+        <v>10.54541081758925</v>
       </c>
       <c r="E43" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F43" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>39.50434413269563</v>
+        <v>6.41945592156304</v>
       </c>
       <c r="D44" t="n">
-        <v>11.81892205409731</v>
+        <v>1.920574833790813</v>
       </c>
       <c r="E44" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F44" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>54.15001009068947</v>
+        <v>8.799376639737039</v>
       </c>
       <c r="D45" t="n">
-        <v>13.72815651840479</v>
+        <v>2.230825434240778</v>
       </c>
       <c r="E45" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F45" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>98.22815844403199</v>
+        <v>15.9620757471552</v>
       </c>
       <c r="D46" t="n">
-        <v>63.03592899186414</v>
+        <v>10.24333846117792</v>
       </c>
       <c r="E46" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F46" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>113.3477607037054</v>
+        <v>18.41901111435213</v>
       </c>
       <c r="D47" t="n">
-        <v>79.51583713673368</v>
+        <v>12.92132353471922</v>
       </c>
       <c r="E47" t="n">
-        <v>22.92977370787377</v>
+        <v>3.726088227529487</v>
       </c>
       <c r="F47" t="n">
-        <v>15.96006870772465</v>
+        <v>2.593511165005256</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
